--- a/Team-Data/2013-14/1-29-2013-14.xlsx
+++ b/Team-Data/2013-14/1-29-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>8</v>
@@ -757,7 +824,7 @@
         <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
         <v>8</v>
@@ -769,22 +836,22 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
         <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ2" t="n">
         <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" t="n">
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>0.313</v>
+        <v>0.319</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J3" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M3" t="n">
         <v>19.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.326</v>
+        <v>0.325</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P3" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
         <v>0.767</v>
       </c>
       <c r="R3" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S3" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T3" t="n">
-        <v>42.9</v>
+        <v>42.6</v>
       </c>
       <c r="U3" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.6</v>
@@ -903,7 +970,7 @@
         <v>7.1</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
@@ -912,13 +979,13 @@
         <v>21.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB3" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
@@ -930,7 +997,7 @@
         <v>28</v>
       </c>
       <c r="AG3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH3" t="n">
         <v>29</v>
@@ -939,7 +1006,7 @@
         <v>24</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK3" t="n">
         <v>26</v>
@@ -954,43 +1021,43 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
         <v>25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT3" t="n">
         <v>21</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>17</v>
       </c>
       <c r="AU3" t="n">
         <v>29</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>24</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
         <v>27</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>18</v>
@@ -1133,13 +1200,13 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
         <v>13</v>
@@ -1160,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.426</v>
+        <v>0.413</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1240,28 +1307,28 @@
         <v>0.349</v>
       </c>
       <c r="O5" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P5" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0.73</v>
       </c>
       <c r="R5" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T5" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="U5" t="n">
         <v>20.3</v>
       </c>
       <c r="V5" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W5" t="n">
         <v>6.2</v>
@@ -1270,31 +1337,31 @@
         <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.1</v>
+        <v>-3.2</v>
       </c>
       <c r="AD5" t="n">
         <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>14</v>
@@ -1303,7 +1370,7 @@
         <v>28</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1321,22 +1388,22 @@
         <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
         <v>23</v>
       </c>
       <c r="AU5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
@@ -1348,7 +1415,7 @@
         <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -1389,34 +1456,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
         <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
         <v>48.9</v>
       </c>
       <c r="I6" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J6" t="n">
         <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.426</v>
+        <v>0.425</v>
       </c>
       <c r="L6" t="n">
         <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="N6" t="n">
         <v>0.342</v>
@@ -1434,49 +1501,49 @@
         <v>12.1</v>
       </c>
       <c r="S6" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U6" t="n">
         <v>22.4</v>
       </c>
       <c r="V6" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
         <v>92.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
@@ -1485,13 +1552,13 @@
         <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM6" t="n">
         <v>27</v>
@@ -1512,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
@@ -1521,10 +1588,10 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
@@ -1661,10 +1728,10 @@
         <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ7" t="n">
         <v>5</v>
@@ -1682,7 +1749,7 @@
         <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
         <v>19</v>
@@ -1703,16 +1770,16 @@
         <v>28</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
       </c>
       <c r="AY7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ7" t="n">
         <v>8</v>
@@ -1721,7 +1788,7 @@
         <v>21</v>
       </c>
       <c r="BB7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
         <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>0.553</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1771,37 +1838,37 @@
         <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.472</v>
       </c>
       <c r="L8" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M8" t="n">
         <v>22.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.376</v>
+        <v>0.378</v>
       </c>
       <c r="O8" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="P8" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
       <c r="R8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S8" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T8" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="U8" t="n">
         <v>23.4</v>
@@ -1810,7 +1877,7 @@
         <v>13.9</v>
       </c>
       <c r="W8" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>4.2</v>
@@ -1819,13 +1886,13 @@
         <v>3.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.1</v>
+        <v>103.9</v>
       </c>
       <c r="AC8" t="n">
         <v>1.4</v>
@@ -1834,16 +1901,16 @@
         <v>4</v>
       </c>
       <c r="AE8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF8" t="n">
         <v>10</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1852,7 +1919,7 @@
         <v>13</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
         <v>8</v>
@@ -1861,13 +1928,13 @@
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AP8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1885,7 +1952,7 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1900,10 +1967,10 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.512</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
@@ -1953,43 +2020,43 @@
         <v>38.3</v>
       </c>
       <c r="J9" t="n">
-        <v>85</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.451</v>
+        <v>0.453</v>
       </c>
       <c r="L9" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O9" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P9" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="R9" t="n">
         <v>12</v>
       </c>
       <c r="S9" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="T9" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U9" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V9" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W9" t="n">
         <v>7.2</v>
@@ -1998,46 +2065,46 @@
         <v>5.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.9</v>
+        <v>104</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
         <v>14</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>16</v>
       </c>
       <c r="AH9" t="n">
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
         <v>6</v>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2046,7 +2113,7 @@
         <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP9" t="n">
         <v>4</v>
@@ -2055,10 +2122,10 @@
         <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>5</v>
@@ -2067,16 +2134,16 @@
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ9" t="n">
         <v>29</v>
@@ -2085,7 +2152,7 @@
         <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
         <v>14</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2216,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>28</v>
@@ -2231,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2240,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2401,16 +2468,16 @@
         <v>7</v>
       </c>
       <c r="AL11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2425,10 +2492,10 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
         <v>29</v>
@@ -2437,7 +2504,7 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>14</v>
@@ -2446,7 +2513,7 @@
         <v>25</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
         <v>11</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -2481,79 +2548,79 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.646</v>
+        <v>0.638</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J12" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.471</v>
+        <v>0.469</v>
       </c>
       <c r="L12" t="n">
         <v>9</v>
       </c>
       <c r="M12" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O12" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="P12" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="T12" t="n">
         <v>45.1</v>
       </c>
       <c r="U12" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V12" t="n">
         <v>16.1</v>
       </c>
       <c r="W12" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y12" t="n">
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>105</v>
+        <v>104.8</v>
       </c>
       <c r="AC12" t="n">
         <v>3.4</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2610,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV12" t="n">
         <v>28</v>
@@ -2622,10 +2689,10 @@
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>8.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2771,10 +2838,10 @@
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -2798,7 +2865,7 @@
         <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>5</v>
@@ -2807,13 +2874,13 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC13" t="n">
         <v>1</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.681</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,43 +2930,43 @@
         <v>38.5</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.469</v>
       </c>
       <c r="L14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M14" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="N14" t="n">
         <v>0.348</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="P14" t="n">
-        <v>28.7</v>
+        <v>28.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="R14" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S14" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T14" t="n">
         <v>42.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="V14" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W14" t="n">
         <v>8.300000000000001</v>
@@ -2911,22 +2978,22 @@
         <v>3.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.3</v>
+        <v>106.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2941,19 +3008,19 @@
         <v>10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2962,13 +3029,13 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
         <v>17</v>
@@ -2977,25 +3044,25 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
         <v>10</v>
       </c>
       <c r="AX14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -3105,19 +3172,19 @@
         <v>-5.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>25</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
         <v>19</v>
@@ -3126,7 +3193,7 @@
         <v>11</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3135,7 +3202,7 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO15" t="n">
         <v>16</v>
@@ -3144,13 +3211,13 @@
         <v>17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
         <v>20</v>
@@ -3159,25 +3226,25 @@
         <v>11</v>
       </c>
       <c r="AV15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>25</v>
       </c>
       <c r="BB15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.545</v>
+        <v>0.535</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J16" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L16" t="n">
         <v>5.1</v>
@@ -3239,55 +3306,55 @@
         <v>14.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O16" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P16" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R16" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S16" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="T16" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="U16" t="n">
         <v>21.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W16" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X16" t="n">
         <v>4.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3305,10 +3372,10 @@
         <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3323,40 +3390,40 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS16" t="n">
         <v>21</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>15</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
         <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.711</v>
+        <v>0.727</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
@@ -3409,28 +3476,28 @@
         <v>39.1</v>
       </c>
       <c r="J17" t="n">
-        <v>76.7</v>
+        <v>76.8</v>
       </c>
       <c r="K17" t="n">
         <v>0.509</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M17" t="n">
         <v>21.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.37</v>
+        <v>0.374</v>
       </c>
       <c r="O17" t="n">
         <v>18</v>
       </c>
       <c r="P17" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R17" t="n">
         <v>7.2</v>
@@ -3445,46 +3512,46 @@
         <v>23.6</v>
       </c>
       <c r="V17" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W17" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.1</v>
+        <v>104.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3502,7 +3569,7 @@
         <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3520,16 +3587,16 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
         <v>4</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="n">
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>0.178</v>
+        <v>0.182</v>
       </c>
       <c r="H18" t="n">
         <v>48.8</v>
@@ -3591,7 +3658,7 @@
         <v>34.8</v>
       </c>
       <c r="J18" t="n">
-        <v>82.7</v>
+        <v>82.5</v>
       </c>
       <c r="K18" t="n">
         <v>0.421</v>
@@ -3603,34 +3670,34 @@
         <v>20.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="O18" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="P18" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.756</v>
+        <v>0.748</v>
       </c>
       <c r="R18" t="n">
         <v>11.4</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T18" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U18" t="n">
         <v>20.9</v>
       </c>
       <c r="V18" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W18" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X18" t="n">
         <v>5.6</v>
@@ -3639,19 +3706,19 @@
         <v>5.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>91.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>-9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="n">
         <v>30</v>
@@ -3684,16 +3751,16 @@
         <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AP18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
@@ -3705,13 +3772,13 @@
         <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
       </c>
       <c r="AX18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
@@ -3720,7 +3787,7 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -3755,37 +3822,37 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
         <v>22</v>
       </c>
       <c r="G19" t="n">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J19" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.346</v>
+        <v>0.349</v>
       </c>
       <c r="O19" t="n">
         <v>21.1</v>
@@ -3794,16 +3861,16 @@
         <v>26.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.783</v>
+        <v>0.785</v>
       </c>
       <c r="R19" t="n">
         <v>13.1</v>
       </c>
       <c r="S19" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T19" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="U19" t="n">
         <v>23.6</v>
@@ -3812,7 +3879,7 @@
         <v>13.8</v>
       </c>
       <c r="W19" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X19" t="n">
         <v>3.4</v>
@@ -3821,34 +3888,34 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.1</v>
+        <v>106.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
@@ -3863,7 +3930,7 @@
         <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
         <v>2</v>
@@ -3884,13 +3951,13 @@
         <v>4</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
         <v>5</v>
       </c>
       <c r="AW19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
@@ -3905,7 +3972,7 @@
         <v>3</v>
       </c>
       <c r="BB19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -3937,37 +4004,37 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.422</v>
+        <v>0.432</v>
       </c>
       <c r="H20" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M20" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.377</v>
+        <v>0.386</v>
       </c>
       <c r="O20" t="n">
         <v>17.8</v>
@@ -3976,31 +4043,31 @@
         <v>23.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R20" t="n">
         <v>12.5</v>
       </c>
       <c r="S20" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T20" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U20" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="V20" t="n">
         <v>13.9</v>
       </c>
       <c r="W20" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X20" t="n">
         <v>6.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
         <v>22.5</v>
@@ -4009,34 +4076,34 @@
         <v>20.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.2</v>
+        <v>100.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF20" t="n">
         <v>19</v>
       </c>
       <c r="AG20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH20" t="n">
         <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>26</v>
@@ -4045,31 +4112,31 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
         <v>14</v>
       </c>
       <c r="AP20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
         <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>9</v>
@@ -4078,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ20" t="n">
         <v>28</v>
@@ -4087,7 +4154,7 @@
         <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC20" t="n">
         <v>18</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
@@ -4209,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4224,16 +4291,16 @@
         <v>7</v>
       </c>
       <c r="AM21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN21" t="n">
         <v>13</v>
       </c>
       <c r="AO21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ21" t="n">
         <v>14</v>
@@ -4242,7 +4309,7 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
@@ -4257,7 +4324,7 @@
         <v>12</v>
       </c>
       <c r="AX21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY21" t="n">
         <v>5</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>0.787</v>
+        <v>0.783</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
@@ -4319,37 +4386,37 @@
         <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.361</v>
+        <v>0.354</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="P22" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.803</v>
+        <v>0.804</v>
       </c>
       <c r="R22" t="n">
         <v>11.2</v>
       </c>
       <c r="S22" t="n">
-        <v>34.6</v>
+        <v>34.9</v>
       </c>
       <c r="T22" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="U22" t="n">
         <v>21.5</v>
@@ -4358,25 +4425,25 @@
         <v>15.6</v>
       </c>
       <c r="W22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X22" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y22" t="n">
         <v>3.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.6</v>
+        <v>105.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD22" t="n">
         <v>4</v>
@@ -4394,28 +4461,28 @@
         <v>25</v>
       </c>
       <c r="AI22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK22" t="n">
         <v>4</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>3</v>
-      </c>
       <c r="AL22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM22" t="n">
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO22" t="n">
         <v>4</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4427,13 +4494,13 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="n">
         <v>16</v>
       </c>
       <c r="AV22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW22" t="n">
         <v>11</v>
@@ -4454,7 +4521,7 @@
         <v>4</v>
       </c>
       <c r="BC22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -4483,64 +4550,64 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
         <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>0.255</v>
+        <v>0.261</v>
       </c>
       <c r="H23" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I23" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J23" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.44</v>
+        <v>0.443</v>
       </c>
       <c r="L23" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M23" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N23" t="n">
         <v>0.345</v>
       </c>
       <c r="O23" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P23" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R23" t="n">
         <v>9.1</v>
       </c>
       <c r="S23" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T23" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U23" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="W23" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X23" t="n">
         <v>4.1</v>
@@ -4549,16 +4616,16 @@
         <v>6</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
         <v>19</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.1</v>
+        <v>-5.9</v>
       </c>
       <c r="AD23" t="n">
         <v>4</v>
@@ -4576,34 +4643,34 @@
         <v>6</v>
       </c>
       <c r="AI23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>23</v>
       </c>
-      <c r="AJ23" t="n">
-        <v>22</v>
-      </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM23" t="n">
         <v>17</v>
       </c>
       <c r="AN23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO23" t="n">
         <v>20</v>
       </c>
       <c r="AP23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS23" t="n">
         <v>8</v>
@@ -4612,13 +4679,13 @@
         <v>22</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>28</v>
@@ -4633,7 +4700,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
         <v>27</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -4665,22 +4732,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F24" t="n">
         <v>31</v>
       </c>
       <c r="G24" t="n">
-        <v>0.326</v>
+        <v>0.311</v>
       </c>
       <c r="H24" t="n">
         <v>48.8</v>
       </c>
       <c r="I24" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J24" t="n">
         <v>88.5</v>
@@ -4698,31 +4765,31 @@
         <v>0.317</v>
       </c>
       <c r="O24" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P24" t="n">
         <v>23.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.711</v>
+        <v>0.715</v>
       </c>
       <c r="R24" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S24" t="n">
         <v>32.8</v>
       </c>
       <c r="T24" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U24" t="n">
         <v>22.6</v>
       </c>
       <c r="V24" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="W24" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X24" t="n">
         <v>4.2</v>
@@ -4731,28 +4798,28 @@
         <v>7.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA24" t="n">
         <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF24" t="n">
         <v>27</v>
       </c>
       <c r="AG24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH24" t="n">
         <v>5</v>
@@ -4776,7 +4843,7 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
         <v>15</v>
@@ -4788,10 +4855,10 @@
         <v>11</v>
       </c>
       <c r="AS24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -4800,7 +4867,7 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX24" t="n">
         <v>24</v>
@@ -4809,7 +4876,7 @@
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -4847,58 +4914,58 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" t="n">
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6</v>
+        <v>0.591</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L25" t="n">
         <v>9.4</v>
       </c>
       <c r="M25" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.37</v>
+        <v>0.367</v>
       </c>
       <c r="O25" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="P25" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.757</v>
+        <v>0.752</v>
       </c>
       <c r="R25" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S25" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T25" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="U25" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="V25" t="n">
         <v>15</v>
@@ -4913,22 +4980,22 @@
         <v>4.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>105</v>
+        <v>104.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
@@ -4937,43 +5004,43 @@
         <v>8</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>8</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU25" t="n">
         <v>30</v>
@@ -4982,7 +5049,7 @@
         <v>16</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -4991,7 +5058,7 @@
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
         <v>11</v>
@@ -5000,7 +5067,7 @@
         <v>6</v>
       </c>
       <c r="BC25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
       </c>
       <c r="AF26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
         <v>17</v>
@@ -5125,10 +5192,10 @@
         <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
         <v>9</v>
@@ -5152,7 +5219,7 @@
         <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -5211,91 +5278,91 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G27" t="n">
-        <v>0.333</v>
+        <v>0.341</v>
       </c>
       <c r="H27" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I27" t="n">
         <v>37.6</v>
       </c>
       <c r="J27" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L27" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
         <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="O27" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="P27" t="n">
-        <v>25.6</v>
+        <v>26</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R27" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S27" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="T27" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
       <c r="U27" t="n">
         <v>19.9</v>
       </c>
       <c r="V27" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.9</v>
+        <v>102.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>26</v>
@@ -5304,7 +5371,7 @@
         <v>11</v>
       </c>
       <c r="AI27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ27" t="n">
         <v>12</v>
@@ -5325,13 +5392,13 @@
         <v>5</v>
       </c>
       <c r="AP27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS27" t="n">
         <v>17</v>
@@ -5346,7 +5413,7 @@
         <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -5393,34 +5460,34 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" t="n">
         <v>33</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
-        <v>0.717</v>
+        <v>0.733</v>
       </c>
       <c r="H28" t="n">
         <v>48.1</v>
       </c>
       <c r="I28" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="J28" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.492</v>
+        <v>0.493</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="N28" t="n">
         <v>0.402</v>
@@ -5429,49 +5496,49 @@
         <v>14.8</v>
       </c>
       <c r="P28" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.769</v>
+        <v>0.766</v>
       </c>
       <c r="R28" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="U28" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X28" t="n">
         <v>4.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>104</v>
+        <v>104.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5498,40 +5565,40 @@
         <v>12</v>
       </c>
       <c r="AM28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP28" t="n">
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY28" t="n">
         <v>17</v>
@@ -5540,13 +5607,13 @@
         <v>2</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F29" t="n">
         <v>21</v>
       </c>
       <c r="G29" t="n">
-        <v>0.533</v>
+        <v>0.523</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
@@ -5593,25 +5660,25 @@
         <v>36</v>
       </c>
       <c r="J29" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K29" t="n">
         <v>0.438</v>
       </c>
       <c r="L29" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="O29" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P29" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q29" t="n">
         <v>0.771</v>
@@ -5620,16 +5687,16 @@
         <v>12</v>
       </c>
       <c r="S29" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T29" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="U29" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V29" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W29" t="n">
         <v>7</v>
@@ -5641,43 +5708,43 @@
         <v>4.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB29" t="n">
         <v>99.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
       </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG29" t="n">
         <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK29" t="n">
         <v>24</v>
       </c>
       <c r="AL29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5686,7 +5753,7 @@
         <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
         <v>10</v>
@@ -5695,16 +5762,16 @@
         <v>7</v>
       </c>
       <c r="AR29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT29" t="n">
         <v>13</v>
       </c>
       <c r="AU29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5713,7 +5780,7 @@
         <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
         <v>13</v>
@@ -5722,7 +5789,7 @@
         <v>26</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -5847,7 +5914,7 @@
         <v>23</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
@@ -5856,7 +5923,7 @@
         <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,19 +5932,19 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>18</v>
       </c>
-      <c r="AO30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>20</v>
-      </c>
       <c r="AR30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5886,22 +5953,22 @@
         <v>24</v>
       </c>
       <c r="AU30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
@@ -5939,58 +6006,58 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" t="n">
         <v>22</v>
       </c>
       <c r="F31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G31" t="n">
-        <v>0.489</v>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
       </c>
       <c r="I31" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J31" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K31" t="n">
-        <v>0.449</v>
+        <v>0.447</v>
       </c>
       <c r="L31" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M31" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.376</v>
+        <v>0.382</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.73</v>
+        <v>0.732</v>
       </c>
       <c r="R31" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S31" t="n">
         <v>32</v>
       </c>
       <c r="T31" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U31" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="V31" t="n">
         <v>15.3</v>
@@ -6002,64 +6069,64 @@
         <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>3</v>
       </c>
       <c r="AI31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL31" t="n">
         <v>15</v>
       </c>
-      <c r="AJ31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>16</v>
-      </c>
       <c r="AM31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
       </c>
       <c r="AP31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>24</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>25</v>
-      </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS31" t="n">
         <v>15</v>
@@ -6068,16 +6135,16 @@
         <v>16</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV31" t="n">
         <v>21</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6086,10 +6153,10 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-29-2013-14</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
